--- a/src/test/resources/excel.xlsx
+++ b/src/test/resources/excel.xlsx
@@ -7,19 +7,15 @@
     <workbookView xWindow="240" yWindow="75" windowWidth="20055" windowHeight="7935"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="PostiveCases" sheetId="1" r:id="rId1"/>
+    <sheet name="NegativeCases" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Translation</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>germany</t>
   </si>
@@ -27,15 +23,44 @@
     <t>alemania</t>
   </si>
   <si>
-    <t>Saksamaa</t>
+    <t>deutschland</t>
+  </si>
+  <si>
+    <t>allemagne</t>
+  </si>
+  <si>
+    <t>saksamaa</t>
+  </si>
+  <si>
+    <t>Translation-Valid</t>
+  </si>
+  <si>
+    <t>Translation-Invalid</t>
+  </si>
+  <si>
+    <t>xyzcountry</t>
+  </si>
+  <si>
+    <t>!@#$%</t>
+  </si>
+  <si>
+    <t>verylongstringverylongstringverylongstring</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -63,8 +88,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -359,20 +385,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -385,25 +411,56 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>